--- a/hasil_eksperimen.xlsx
+++ b/hasil_eksperimen.xlsx
@@ -523,34 +523,34 @@
         <v>0.1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.75431</v>
+        <v>0.753385</v>
       </c>
       <c r="G2" t="n">
-        <v>0.50862</v>
+        <v>0.5067700000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>0.751006</v>
+        <v>0.751363</v>
       </c>
       <c r="I2" t="n">
-        <v>12.11</v>
+        <v>6.56</v>
       </c>
       <c r="J2" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1249</v>
+        <v>0.121</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1409</v>
+        <v>0.1374</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0742</v>
+        <v>0.0678</v>
       </c>
       <c r="N2" t="n">
-        <v>0.001</v>
+        <v>0.0261</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6589</v>
+        <v>0.6477000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -570,34 +570,34 @@
         <v>0.1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.75439</v>
+        <v>0.754227</v>
       </c>
       <c r="G3" t="n">
-        <v>0.508781</v>
+        <v>0.508455</v>
       </c>
       <c r="H3" t="n">
-        <v>0.753149</v>
+        <v>0.752948</v>
       </c>
       <c r="I3" t="n">
-        <v>5.51</v>
+        <v>22.2</v>
       </c>
       <c r="J3" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1241</v>
+        <v>0.1237</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1407</v>
+        <v>0.14</v>
       </c>
       <c r="M3" t="n">
-        <v>0.07049999999999999</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0003</v>
+        <v>0.0054</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6645</v>
+        <v>0.6633</v>
       </c>
     </row>
     <row r="4">
@@ -617,34 +617,34 @@
         <v>0.2</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7543609999999999</v>
+        <v>0.754391</v>
       </c>
       <c r="G4" t="n">
-        <v>0.508722</v>
+        <v>0.508782</v>
       </c>
       <c r="H4" t="n">
-        <v>0.753985</v>
+        <v>0.754023</v>
       </c>
       <c r="I4" t="n">
-        <v>84.05</v>
+        <v>78.66</v>
       </c>
       <c r="J4" t="n">
-        <v>136</v>
+        <v>102</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1207</v>
+        <v>0.1233</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1383</v>
+        <v>0.1407</v>
       </c>
       <c r="M4" t="n">
-        <v>0.066</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0015</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6735</v>
+        <v>0.6663</v>
       </c>
     </row>
     <row r="5">
@@ -664,34 +664,34 @@
         <v>0.15</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7544110000000001</v>
+        <v>0.754352</v>
       </c>
       <c r="G5" t="n">
-        <v>0.508822</v>
+        <v>0.508705</v>
       </c>
       <c r="H5" t="n">
-        <v>0.754062</v>
+        <v>0.753902</v>
       </c>
       <c r="I5" t="n">
-        <v>169.21</v>
+        <v>149.34</v>
       </c>
       <c r="J5" t="n">
-        <v>74</v>
+        <v>177</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1238</v>
+        <v>0.1239</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1409</v>
+        <v>0.1405</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0689</v>
+        <v>0.0692</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>0.0016</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6664</v>
+        <v>0.6647999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -711,34 +711,34 @@
         <v>0.25</v>
       </c>
       <c r="F6" t="n">
-        <v>0.754022</v>
+        <v>0.754389</v>
       </c>
       <c r="G6" t="n">
-        <v>0.508045</v>
+        <v>0.508778</v>
       </c>
       <c r="H6" t="n">
-        <v>0.753595</v>
+        <v>0.753601</v>
       </c>
       <c r="I6" t="n">
-        <v>27.24</v>
+        <v>36.03</v>
       </c>
       <c r="J6" t="n">
         <v>80</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1201</v>
+        <v>0.1194</v>
       </c>
       <c r="L6" t="n">
-        <v>0.137</v>
+        <v>0.1351</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0644</v>
+        <v>0.0556</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0108</v>
+        <v>0.0012</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6677</v>
+        <v>0.6886</v>
       </c>
     </row>
   </sheetData>
@@ -792,19 +792,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.7370871177805716</v>
+        <v>0.7352617063650265</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7262787742060964</v>
+        <v>0.7456607151507918</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7417404943753481</v>
+        <v>0.7459277188681539</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7430104879480434</v>
+        <v>0.7396391835251391</v>
       </c>
       <c r="F2" t="n">
-        <v>0.747186840966986</v>
+        <v>0.7437508771914838</v>
       </c>
     </row>
     <row r="3">
@@ -812,19 +812,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.7424565590789387</v>
+        <v>0.7379046976970823</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7293807381564652</v>
+        <v>0.7456607151507918</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7417404943753481</v>
+        <v>0.7459277188681539</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7430104879480434</v>
+        <v>0.7396391835251391</v>
       </c>
       <c r="F3" t="n">
-        <v>0.747186840966986</v>
+        <v>0.7437508771914838</v>
       </c>
     </row>
     <row r="4">
@@ -832,19 +832,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.7427937426605431</v>
+        <v>0.7387001710705028</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7476513495332014</v>
+        <v>0.7456607151507918</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7468747823632569</v>
+        <v>0.7459277188681539</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7477408004546062</v>
+        <v>0.7464756640880166</v>
       </c>
       <c r="F4" t="n">
-        <v>0.749237377628254</v>
+        <v>0.7446118620657683</v>
       </c>
     </row>
     <row r="5">
@@ -852,19 +852,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.7437041098489338</v>
+        <v>0.740681779918579</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7476513495332014</v>
+        <v>0.7467943207370439</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7468747823632569</v>
+        <v>0.7506537876329107</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7491045632474302</v>
+        <v>0.7464756640880166</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7497715072948352</v>
+        <v>0.7494508362765632</v>
       </c>
     </row>
     <row r="6">
@@ -872,19 +872,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.7458238565251201</v>
+        <v>0.7426658426752422</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7476513495332014</v>
+        <v>0.7487552760838079</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7477173634434467</v>
+        <v>0.7517059294634429</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7491045632474302</v>
+        <v>0.7504860867446776</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7520587971822356</v>
+        <v>0.7528862757439458</v>
       </c>
     </row>
     <row r="7">
@@ -892,19 +892,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.7460657655224257</v>
+        <v>0.744075655282458</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7476513495332014</v>
+        <v>0.7487552760838079</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7521281021404591</v>
+        <v>0.7517059294634429</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7504187097669626</v>
+        <v>0.7519340681932293</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7520587971822356</v>
+        <v>0.7528862757439458</v>
       </c>
     </row>
     <row r="8">
@@ -912,19 +912,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.7494286359217031</v>
+        <v>0.744075655282458</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7476513495332014</v>
+        <v>0.7492784184097114</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7521281021404591</v>
+        <v>0.7517059294634429</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7516081521807654</v>
+        <v>0.7519340681932293</v>
       </c>
       <c r="F8" t="n">
-        <v>0.752270205145702</v>
+        <v>0.7528862757439458</v>
       </c>
     </row>
     <row r="9">
@@ -932,19 +932,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.7494286359217031</v>
+        <v>0.7524354922558192</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7479652239369938</v>
+        <v>0.7494676494149535</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7521281021404591</v>
+        <v>0.7525988268165665</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7518821571706744</v>
+        <v>0.7519340681932293</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7529901734707334</v>
+        <v>0.7529747151434458</v>
       </c>
     </row>
     <row r="10">
@@ -952,19 +952,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7494286359217031</v>
+        <v>0.7524354922558192</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7522927124993055</v>
+        <v>0.7498358393819013</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7542095210064912</v>
+        <v>0.7535975510307737</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7528453335884824</v>
+        <v>0.7519340681932293</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7533714347679266</v>
+        <v>0.7535570115615644</v>
       </c>
     </row>
     <row r="11">
@@ -972,19 +972,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7495495768682281</v>
+        <v>0.7524354922558192</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7522927124993055</v>
+        <v>0.7500742854211832</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7542095210064912</v>
+        <v>0.7537678981401924</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7528453335884824</v>
+        <v>0.7525995395684653</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7534487336215623</v>
+        <v>0.7535570115615644</v>
       </c>
     </row>
     <row r="12">
@@ -992,19 +992,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.7504703361404463</v>
+        <v>0.7524354922558192</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7522927124993055</v>
+        <v>0.7501754548119999</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7542357095697235</v>
+        <v>0.7538488361894005</v>
       </c>
       <c r="E12" t="n">
-        <v>0.7528495618878025</v>
+        <v>0.7526093559251921</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7536338348426904</v>
+        <v>0.7535948048072344</v>
       </c>
     </row>
     <row r="13">
@@ -1012,19 +1012,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.7505740340813651</v>
+        <v>0.7527748941561523</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7524075956680549</v>
+        <v>0.7503809122372576</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7542357095697235</v>
+        <v>0.7539269301141936</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7530588400111957</v>
+        <v>0.7528778526661614</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7538892473463745</v>
+        <v>0.753611931724314</v>
       </c>
     </row>
     <row r="14">
@@ -1032,19 +1032,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.7509641459692248</v>
+        <v>0.7528341945631745</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7527407296399922</v>
+        <v>0.7505289159586569</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7542535449132914</v>
+        <v>0.7539269301141936</v>
       </c>
       <c r="E14" t="n">
-        <v>0.7532776606511318</v>
+        <v>0.7532271777452046</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7538892473463745</v>
+        <v>0.753611931724314</v>
       </c>
     </row>
     <row r="15">
@@ -1052,19 +1052,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7509768044845815</v>
+        <v>0.7529547878159715</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7531541138850339</v>
+        <v>0.7505464470857088</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7542853327795349</v>
+        <v>0.753930112913141</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7533181668856297</v>
+        <v>0.7533723420533643</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7538892473463745</v>
+        <v>0.7536297504187712</v>
       </c>
     </row>
     <row r="16">
@@ -1072,19 +1072,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.7513704197813922</v>
+        <v>0.7530555205579104</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7531541138850339</v>
+        <v>0.7506372078942189</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7543120949777709</v>
+        <v>0.7540022983268045</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7533987705760949</v>
+        <v>0.7533868843010971</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7538892473463745</v>
+        <v>0.7536300092874997</v>
       </c>
     </row>
     <row r="17">
@@ -1092,19 +1092,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.7513704197813922</v>
+        <v>0.7530555205579104</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7531686169646068</v>
+        <v>0.7523272227523612</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7543131270992754</v>
+        <v>0.7540086897078827</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7533987705760949</v>
+        <v>0.7534059980172463</v>
       </c>
       <c r="F17" t="n">
-        <v>0.753904291753252</v>
+        <v>0.7536333707012505</v>
       </c>
     </row>
     <row r="18">
@@ -1112,19 +1112,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.7513704197813922</v>
+        <v>0.7530555205579104</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7531701516428981</v>
+        <v>0.7523272227523612</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7543138581423068</v>
+        <v>0.754022162317586</v>
       </c>
       <c r="E18" t="n">
-        <v>0.753452801068467</v>
+        <v>0.7534690915100393</v>
       </c>
       <c r="F18" t="n">
-        <v>0.753914242454319</v>
+        <v>0.7536468988877366</v>
       </c>
     </row>
     <row r="19">
@@ -1132,19 +1132,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.7513704197813922</v>
+        <v>0.7530584670827606</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7531996572134083</v>
+        <v>0.7523272227523612</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7543191128904563</v>
+        <v>0.7540250123769796</v>
       </c>
       <c r="E19" t="n">
-        <v>0.753479667499954</v>
+        <v>0.7535326261012361</v>
       </c>
       <c r="F19" t="n">
-        <v>0.753914242454319</v>
+        <v>0.7536493953844274</v>
       </c>
     </row>
     <row r="20">
@@ -1152,19 +1152,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.7513843971711334</v>
+        <v>0.7530605035075745</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7532029725257618</v>
+        <v>0.7524409275181042</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7543191128904563</v>
+        <v>0.7540250123769796</v>
       </c>
       <c r="E20" t="n">
-        <v>0.753479667499954</v>
+        <v>0.7535326261012361</v>
       </c>
       <c r="F20" t="n">
-        <v>0.753914242454319</v>
+        <v>0.7536509346553394</v>
       </c>
     </row>
     <row r="21">
@@ -1172,19 +1172,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.7513843971711334</v>
+        <v>0.7530792537335758</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7532240667339842</v>
+        <v>0.7527515994671586</v>
       </c>
       <c r="D21" t="n">
-        <v>0.754319619669493</v>
+        <v>0.7540271724415961</v>
       </c>
       <c r="E21" t="n">
-        <v>0.753479667499954</v>
+        <v>0.7535326261012361</v>
       </c>
       <c r="F21" t="n">
-        <v>0.753914242454319</v>
+        <v>0.753676985179311</v>
       </c>
     </row>
     <row r="22">
@@ -1192,19 +1192,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>0.7513854641025187</v>
+        <v>0.7530844079400359</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7532428782268754</v>
+        <v>0.7529620807853297</v>
       </c>
       <c r="D22" t="n">
-        <v>0.7543246488429312</v>
+        <v>0.754027186988725</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7534886786522459</v>
+        <v>0.7535750003465695</v>
       </c>
       <c r="F22" t="n">
-        <v>0.753914242454319</v>
+        <v>0.753676985179311</v>
       </c>
     </row>
     <row r="23">
@@ -1212,19 +1212,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>0.7513864979968502</v>
+        <v>0.7530844079400359</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7532428782268754</v>
+        <v>0.7532859298397837</v>
       </c>
       <c r="D23" t="n">
-        <v>0.7543246488429312</v>
+        <v>0.7540289482612261</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7534935915983553</v>
+        <v>0.7535774473114425</v>
       </c>
       <c r="F23" t="n">
-        <v>0.753914990601309</v>
+        <v>0.7536882672475889</v>
       </c>
     </row>
     <row r="24">
@@ -1232,19 +1232,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>0.7513905968922736</v>
+        <v>0.7530872835356792</v>
       </c>
       <c r="C24" t="n">
-        <v>0.7532469406241795</v>
+        <v>0.7533283259494852</v>
       </c>
       <c r="D24" t="n">
-        <v>0.7543255858895246</v>
+        <v>0.7540295797154735</v>
       </c>
       <c r="E24" t="n">
-        <v>0.7535027097643342</v>
+        <v>0.7535831741617957</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7539166303609857</v>
+        <v>0.7536882672475889</v>
       </c>
     </row>
     <row r="25">
@@ -1252,19 +1252,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>0.7516760924230179</v>
+        <v>0.7530872835356792</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7532485243657109</v>
+        <v>0.7534882766197581</v>
       </c>
       <c r="D25" t="n">
-        <v>0.7543260113162622</v>
+        <v>0.7540303983936948</v>
       </c>
       <c r="E25" t="n">
-        <v>0.7535136088597434</v>
+        <v>0.7535865737437735</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7539206506504273</v>
+        <v>0.7536884434572253</v>
       </c>
     </row>
     <row r="26">
@@ -1272,19 +1272,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>0.7516760924230179</v>
+        <v>0.7530928283761846</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7532520838881143</v>
+        <v>0.7535123812089893</v>
       </c>
       <c r="D26" t="n">
-        <v>0.7543272486486057</v>
+        <v>0.7540308185216473</v>
       </c>
       <c r="E26" t="n">
-        <v>0.7535136088597434</v>
+        <v>0.7542141014689054</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7539227738174469</v>
+        <v>0.7536888293707933</v>
       </c>
     </row>
     <row r="27">
@@ -1292,19 +1292,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>0.7516763898848022</v>
+        <v>0.7530928283761846</v>
       </c>
       <c r="C27" t="n">
-        <v>0.7532584973257815</v>
+        <v>0.7535124147304633</v>
       </c>
       <c r="D27" t="n">
-        <v>0.7543272486486057</v>
+        <v>0.7540310699873494</v>
       </c>
       <c r="E27" t="n">
-        <v>0.7535796504994262</v>
+        <v>0.7542141014689054</v>
       </c>
       <c r="F27" t="n">
-        <v>0.753924116478872</v>
+        <v>0.7536905474869822</v>
       </c>
     </row>
     <row r="28">
@@ -1312,19 +1312,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>0.751680772553117</v>
+        <v>0.7530932127689098</v>
       </c>
       <c r="C28" t="n">
-        <v>0.7532584973257815</v>
+        <v>0.7535138492131048</v>
       </c>
       <c r="D28" t="n">
-        <v>0.7543272993761031</v>
+        <v>0.7540312021645247</v>
       </c>
       <c r="E28" t="n">
-        <v>0.7535839539827591</v>
+        <v>0.75421748644362</v>
       </c>
       <c r="F28" t="n">
-        <v>0.7539278063981019</v>
+        <v>0.7536928048397189</v>
       </c>
     </row>
     <row r="29">
@@ -1332,19 +1332,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>0.751680772553117</v>
+        <v>0.7530941840570342</v>
       </c>
       <c r="C29" t="n">
-        <v>0.7532975171733974</v>
+        <v>0.7535143717808435</v>
       </c>
       <c r="D29" t="n">
-        <v>0.7543272993761031</v>
+        <v>0.7540312021645247</v>
       </c>
       <c r="E29" t="n">
-        <v>0.7543977003421288</v>
+        <v>0.7542178130715702</v>
       </c>
       <c r="F29" t="n">
-        <v>0.7539288032354797</v>
+        <v>0.7536928048397189</v>
       </c>
     </row>
     <row r="30">
@@ -1352,19 +1352,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>0.751680772553117</v>
+        <v>0.7530944240162757</v>
       </c>
       <c r="C30" t="n">
-        <v>0.7533292064914918</v>
+        <v>0.7535218470558176</v>
       </c>
       <c r="D30" t="n">
-        <v>0.7543273603803715</v>
+        <v>0.7540313158669991</v>
       </c>
       <c r="E30" t="n">
-        <v>0.7543977003421288</v>
+        <v>0.7542203779447441</v>
       </c>
       <c r="F30" t="n">
-        <v>0.7539306292364101</v>
+        <v>0.7536940899716087</v>
       </c>
     </row>
     <row r="31">
@@ -1372,19 +1372,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>0.751680772553117</v>
+        <v>0.7530944240162757</v>
       </c>
       <c r="C31" t="n">
-        <v>0.7533541687799572</v>
+        <v>0.7535302243099287</v>
       </c>
       <c r="D31" t="n">
-        <v>0.7543276666716265</v>
+        <v>0.7540313158669991</v>
       </c>
       <c r="E31" t="n">
-        <v>0.7543977003421288</v>
+        <v>0.7542225846651449</v>
       </c>
       <c r="F31" t="n">
-        <v>0.7539307213481923</v>
+        <v>0.7541331568248366</v>
       </c>
     </row>
     <row r="32">
@@ -1392,19 +1392,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>0.7516829007383072</v>
+        <v>0.7532174001233874</v>
       </c>
       <c r="C32" t="n">
-        <v>0.7533541687799572</v>
+        <v>0.7535333986472985</v>
       </c>
       <c r="D32" t="n">
-        <v>0.7543325297449495</v>
+        <v>0.7540313316416372</v>
       </c>
       <c r="E32" t="n">
-        <v>0.7543977003421288</v>
+        <v>0.7542272562905934</v>
       </c>
       <c r="F32" t="n">
-        <v>0.7539307213481923</v>
+        <v>0.7541331568248366</v>
       </c>
     </row>
     <row r="33">
@@ -1412,19 +1412,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>0.7516834745015013</v>
+        <v>0.7532799197177082</v>
       </c>
       <c r="C33" t="n">
-        <v>0.7543327519642216</v>
+        <v>0.7535339860164352</v>
       </c>
       <c r="D33" t="n">
-        <v>0.7543325297449495</v>
+        <v>0.7540313658412696</v>
       </c>
       <c r="E33" t="n">
-        <v>0.7543982933784878</v>
+        <v>0.7542292777808373</v>
       </c>
       <c r="F33" t="n">
-        <v>0.7539307213481923</v>
+        <v>0.7541337770977864</v>
       </c>
     </row>
     <row r="34">
@@ -1432,19 +1432,19 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>0.7516837307577334</v>
+        <v>0.7533221623244256</v>
       </c>
       <c r="C34" t="n">
-        <v>0.7543327519642216</v>
+        <v>0.7535348905420827</v>
       </c>
       <c r="D34" t="n">
-        <v>0.7543325297449495</v>
+        <v>0.7540313658412696</v>
       </c>
       <c r="E34" t="n">
-        <v>0.7544023663610844</v>
+        <v>0.7542292777808373</v>
       </c>
       <c r="F34" t="n">
-        <v>0.7539309061515924</v>
+        <v>0.7541340815082278</v>
       </c>
     </row>
     <row r="35">
@@ -1452,19 +1452,19 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>0.7516840698542605</v>
+        <v>0.7533327986891665</v>
       </c>
       <c r="C35" t="n">
-        <v>0.7543579326935426</v>
+        <v>0.7535349526289563</v>
       </c>
       <c r="D35" t="n">
-        <v>0.7543325297449495</v>
+        <v>0.7540313881673116</v>
       </c>
       <c r="E35" t="n">
-        <v>0.7544068835059693</v>
+        <v>0.7542298100332299</v>
       </c>
       <c r="F35" t="n">
-        <v>0.7539309061515924</v>
+        <v>0.7541346872279082</v>
       </c>
     </row>
     <row r="36">
@@ -1472,19 +1472,19 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>0.7516842483463231</v>
+        <v>0.7533327986891665</v>
       </c>
       <c r="C36" t="n">
-        <v>0.7543609895248281</v>
+        <v>0.7535351489920852</v>
       </c>
       <c r="D36" t="n">
-        <v>0.7543325297449495</v>
+        <v>0.7540313881673116</v>
       </c>
       <c r="E36" t="n">
-        <v>0.754408853838608</v>
+        <v>0.7542298100332299</v>
       </c>
       <c r="F36" t="n">
-        <v>0.7539310165549464</v>
+        <v>0.7541346872279082</v>
       </c>
     </row>
     <row r="37">
@@ -1492,19 +1492,19 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>0.7516851399294331</v>
+        <v>0.7533680334988653</v>
       </c>
       <c r="C37" t="n">
-        <v>0.7543702002024208</v>
+        <v>0.7535351707821478</v>
       </c>
       <c r="D37" t="n">
-        <v>0.7543325297449495</v>
+        <v>0.7540313952753696</v>
       </c>
       <c r="E37" t="n">
-        <v>0.7544094461288979</v>
+        <v>0.7542300646871933</v>
       </c>
       <c r="F37" t="n">
-        <v>0.7539310165549464</v>
+        <v>0.7541346872279082</v>
       </c>
     </row>
     <row r="38">
@@ -1512,19 +1512,19 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>0.7516851399294331</v>
+        <v>0.7533680334988653</v>
       </c>
       <c r="C38" t="n">
-        <v>0.7543702002024208</v>
+        <v>0.7535351707821478</v>
       </c>
       <c r="D38" t="n">
-        <v>0.7543337194201494</v>
+        <v>0.7540314291104155</v>
       </c>
       <c r="E38" t="n">
-        <v>0.7544097591283064</v>
+        <v>0.7542307209506611</v>
       </c>
       <c r="F38" t="n">
-        <v>0.7539310165549464</v>
+        <v>0.7541346872279082</v>
       </c>
     </row>
     <row r="39">
@@ -1532,19 +1532,19 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>0.7541446378390422</v>
+        <v>0.7533792162660937</v>
       </c>
       <c r="C39" t="n">
-        <v>0.7543790571477003</v>
+        <v>0.7535352636700121</v>
       </c>
       <c r="D39" t="n">
-        <v>0.7543337194201494</v>
+        <v>0.7540314457454329</v>
       </c>
       <c r="E39" t="n">
-        <v>0.7544099633337887</v>
+        <v>0.7542308852510984</v>
       </c>
       <c r="F39" t="n">
-        <v>0.7539310240380553</v>
+        <v>0.7541350210489044</v>
       </c>
     </row>
     <row r="40">
@@ -1552,19 +1552,19 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>0.7541884387797747</v>
+        <v>0.7533792162660937</v>
       </c>
       <c r="C40" t="n">
-        <v>0.754379953822487</v>
+        <v>0.7535354440725761</v>
       </c>
       <c r="D40" t="n">
-        <v>0.7543356480442487</v>
+        <v>0.7540314472148252</v>
       </c>
       <c r="E40" t="n">
-        <v>0.7544100273431533</v>
+        <v>0.7542313455531947</v>
       </c>
       <c r="F40" t="n">
-        <v>0.7539974030951104</v>
+        <v>0.7541352016315088</v>
       </c>
     </row>
     <row r="41">
@@ -1572,19 +1572,19 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>0.7542710502921474</v>
+        <v>0.7533792162660937</v>
       </c>
       <c r="C41" t="n">
-        <v>0.7543819568411096</v>
+        <v>0.7535354440725761</v>
       </c>
       <c r="D41" t="n">
-        <v>0.7543356480442487</v>
+        <v>0.7540314472148252</v>
       </c>
       <c r="E41" t="n">
-        <v>0.7544100273431533</v>
+        <v>0.7542313455531947</v>
       </c>
       <c r="F41" t="n">
-        <v>0.7539974030951104</v>
+        <v>0.7541357302045708</v>
       </c>
     </row>
     <row r="42">
@@ -1592,19 +1592,19 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>0.7542876202482991</v>
+        <v>0.7533825645066194</v>
       </c>
       <c r="C42" t="n">
-        <v>0.754383176080707</v>
+        <v>0.7535354440725761</v>
       </c>
       <c r="D42" t="n">
-        <v>0.7543358851573227</v>
+        <v>0.7540314472148252</v>
       </c>
       <c r="E42" t="n">
-        <v>0.7544100273431533</v>
+        <v>0.7542313455531947</v>
       </c>
       <c r="F42" t="n">
-        <v>0.7539974030951104</v>
+        <v>0.7541357590389959</v>
       </c>
     </row>
     <row r="43">
@@ -1612,19 +1612,19 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>0.7542876202482991</v>
+        <v>0.7533825645066194</v>
       </c>
       <c r="C43" t="n">
-        <v>0.754383176080707</v>
+        <v>0.7535354440725761</v>
       </c>
       <c r="D43" t="n">
-        <v>0.7543368815775009</v>
+        <v>0.75403145239803</v>
       </c>
       <c r="E43" t="n">
-        <v>0.7544100998156941</v>
+        <v>0.7542313976364647</v>
       </c>
       <c r="F43" t="n">
-        <v>0.7539974030951104</v>
+        <v>0.7541357590389959</v>
       </c>
     </row>
     <row r="44">
@@ -1632,19 +1632,19 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>0.7542971043005438</v>
+        <v>0.7533825645066194</v>
       </c>
       <c r="C44" t="n">
-        <v>0.7543837916715105</v>
+        <v>0.7535354530434266</v>
       </c>
       <c r="D44" t="n">
-        <v>0.7543368815775009</v>
+        <v>0.754217352810133</v>
       </c>
       <c r="E44" t="n">
-        <v>0.7544107972594583</v>
+        <v>0.7542316684820118</v>
       </c>
       <c r="F44" t="n">
-        <v>0.7539980711183278</v>
+        <v>0.7541357590389959</v>
       </c>
     </row>
     <row r="45">
@@ -1652,19 +1652,19 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>0.7542989315383942</v>
+        <v>0.7533829735436761</v>
       </c>
       <c r="C45" t="n">
-        <v>0.7543837916715105</v>
+        <v>0.7535354572630604</v>
       </c>
       <c r="D45" t="n">
-        <v>0.7543379363996625</v>
+        <v>0.754217352810133</v>
       </c>
       <c r="E45" t="n">
-        <v>0.7544107972594583</v>
+        <v>0.7542316684820118</v>
       </c>
       <c r="F45" t="n">
-        <v>0.7539980711183278</v>
+        <v>0.7541818965986287</v>
       </c>
     </row>
     <row r="46">
@@ -1672,19 +1672,19 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>0.7542989315383942</v>
+        <v>0.7533835569025056</v>
       </c>
       <c r="C46" t="n">
-        <v>0.7543844919228166</v>
+        <v>0.7535354572630604</v>
       </c>
       <c r="D46" t="n">
-        <v>0.7543379363996625</v>
+        <v>0.754217352810133</v>
       </c>
       <c r="E46" t="n">
-        <v>0.7544107972594583</v>
+        <v>0.7542316684820118</v>
       </c>
       <c r="F46" t="n">
-        <v>0.7539980711183278</v>
+        <v>0.7541820245406186</v>
       </c>
     </row>
     <row r="47">
@@ -1692,19 +1692,19 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>0.7543057969321968</v>
+        <v>0.7533841933267432</v>
       </c>
       <c r="C47" t="n">
-        <v>0.7543845462846255</v>
+        <v>0.7535354572630604</v>
       </c>
       <c r="D47" t="n">
-        <v>0.7543381907151996</v>
+        <v>0.754217352810133</v>
       </c>
       <c r="E47" t="n">
-        <v>0.7544107972594583</v>
+        <v>0.7542317061249058</v>
       </c>
       <c r="F47" t="n">
-        <v>0.7539982356077071</v>
+        <v>0.7541841563112588</v>
       </c>
     </row>
     <row r="48">
@@ -1712,19 +1712,19 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>0.7543061248928816</v>
+        <v>0.7533844900287616</v>
       </c>
       <c r="C48" t="n">
-        <v>0.7543847286927783</v>
+        <v>0.7535354620975936</v>
       </c>
       <c r="D48" t="n">
-        <v>0.7543381907151996</v>
+        <v>0.754217352810133</v>
       </c>
       <c r="E48" t="n">
-        <v>0.7544107972594583</v>
+        <v>0.7542317061249058</v>
       </c>
       <c r="F48" t="n">
-        <v>0.7539983712855163</v>
+        <v>0.7541844410036842</v>
       </c>
     </row>
     <row r="49">
@@ -1732,19 +1732,19 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>0.7543088300171733</v>
+        <v>0.7533844900287616</v>
       </c>
       <c r="C49" t="n">
-        <v>0.7543857776586996</v>
+        <v>0.7535354656885935</v>
       </c>
       <c r="D49" t="n">
-        <v>0.7543383540996278</v>
+        <v>0.754217352810133</v>
       </c>
       <c r="E49" t="n">
-        <v>0.7544107972594583</v>
+        <v>0.7542317061249058</v>
       </c>
       <c r="F49" t="n">
-        <v>0.7539986140117851</v>
+        <v>0.7541848544077138</v>
       </c>
     </row>
     <row r="50">
@@ -1752,19 +1752,19 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>0.7543094671980144</v>
+        <v>0.753385049196758</v>
       </c>
       <c r="C50" t="n">
-        <v>0.7543857776586996</v>
+        <v>0.7535354656885935</v>
       </c>
       <c r="D50" t="n">
-        <v>0.754338525966926</v>
+        <v>0.754217352810133</v>
       </c>
       <c r="E50" t="n">
-        <v>0.7544107972594583</v>
+        <v>0.7542317061249058</v>
       </c>
       <c r="F50" t="n">
-        <v>0.7539986140117851</v>
+        <v>0.7543527760954249</v>
       </c>
     </row>
     <row r="51">
@@ -1772,19 +1772,19 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>0.7543097538195791</v>
+        <v>0.753385049196758</v>
       </c>
       <c r="C51" t="n">
-        <v>0.7543864465232204</v>
+        <v>0.7535499022198753</v>
       </c>
       <c r="D51" t="n">
-        <v>0.7543388267939964</v>
+        <v>0.7542175536510204</v>
       </c>
       <c r="E51" t="n">
-        <v>0.7544107972594583</v>
+        <v>0.7542317298636572</v>
       </c>
       <c r="F51" t="n">
-        <v>0.7540049850040733</v>
+        <v>0.7543527760954249</v>
       </c>
     </row>
     <row r="52">
@@ -1793,16 +1793,16 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>0.7543870926409023</v>
+        <v>0.7535625316563994</v>
       </c>
       <c r="D52" t="n">
-        <v>0.7543388841782332</v>
+        <v>0.7542175536510204</v>
       </c>
       <c r="E52" t="n">
-        <v>0.7544107972594583</v>
+        <v>0.7542317542174168</v>
       </c>
       <c r="F52" t="n">
-        <v>0.7540069293681106</v>
+        <v>0.7543527760954249</v>
       </c>
     </row>
     <row r="53">
@@ -1811,16 +1811,16 @@
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
-        <v>0.7543874063877969</v>
+        <v>0.7535625316563994</v>
       </c>
       <c r="D53" t="n">
-        <v>0.7543388841782332</v>
+        <v>0.7542175536510204</v>
       </c>
       <c r="E53" t="n">
-        <v>0.7544107972594583</v>
+        <v>0.754231765980367</v>
       </c>
       <c r="F53" t="n">
-        <v>0.7540069293681106</v>
+        <v>0.7543527760954249</v>
       </c>
     </row>
     <row r="54">
@@ -1829,16 +1829,16 @@
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
-        <v>0.7543890917307174</v>
+        <v>0.7535721844648622</v>
       </c>
       <c r="D54" t="n">
-        <v>0.7543388841782332</v>
+        <v>0.7542175536510204</v>
       </c>
       <c r="E54" t="n">
-        <v>0.7544107972594583</v>
+        <v>0.7542317701532375</v>
       </c>
       <c r="F54" t="n">
-        <v>0.7540101109328855</v>
+        <v>0.7543531654573412</v>
       </c>
     </row>
     <row r="55">
@@ -1847,16 +1847,16 @@
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
-        <v>0.7543890917307174</v>
+        <v>0.7535838410836622</v>
       </c>
       <c r="D55" t="n">
-        <v>0.7543388841782332</v>
+        <v>0.7542175536510204</v>
       </c>
       <c r="E55" t="n">
-        <v>0.7544107972594583</v>
+        <v>0.7542317701532375</v>
       </c>
       <c r="F55" t="n">
-        <v>0.7540167901770716</v>
+        <v>0.7543531654573412</v>
       </c>
     </row>
     <row r="56">
@@ -1865,16 +1865,16 @@
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
-        <v>0.7543890917307174</v>
+        <v>0.7535873246367569</v>
       </c>
       <c r="D56" t="n">
-        <v>0.7543389334913861</v>
+        <v>0.754217590928274</v>
       </c>
       <c r="E56" t="n">
-        <v>0.7544107972594583</v>
+        <v>0.7542317701532375</v>
       </c>
       <c r="F56" t="n">
-        <v>0.7540167901770716</v>
+        <v>0.754353792612962</v>
       </c>
     </row>
     <row r="57">
@@ -1883,16 +1883,16 @@
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="n">
-        <v>0.7543890917307174</v>
+        <v>0.7535902533615404</v>
       </c>
       <c r="D57" t="n">
-        <v>0.7543389846080328</v>
+        <v>0.7543582394464294</v>
       </c>
       <c r="E57" t="n">
-        <v>0.7544107972594583</v>
+        <v>0.7542317953169434</v>
       </c>
       <c r="F57" t="n">
-        <v>0.7540179225431758</v>
+        <v>0.7543538461609007</v>
       </c>
     </row>
     <row r="58">
@@ -1901,16 +1901,16 @@
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="n">
-        <v>0.7543895161713563</v>
+        <v>0.7535917209717105</v>
       </c>
       <c r="D58" t="n">
-        <v>0.7543391719212815</v>
+        <v>0.7543582394464294</v>
       </c>
       <c r="E58" t="n">
-        <v>0.7544107972594583</v>
+        <v>0.7542317953169434</v>
       </c>
       <c r="F58" t="n">
-        <v>0.754019600444046</v>
+        <v>0.7543548145222676</v>
       </c>
     </row>
     <row r="59">
@@ -1919,16 +1919,16 @@
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="n">
-        <v>0.7543895161713563</v>
+        <v>0.7535931404742541</v>
       </c>
       <c r="D59" t="n">
-        <v>0.7543391719212815</v>
+        <v>0.7543582394464294</v>
       </c>
       <c r="E59" t="n">
-        <v>0.7544107972594583</v>
+        <v>0.7542317953169434</v>
       </c>
       <c r="F59" t="n">
-        <v>0.754019600444046</v>
+        <v>0.7543548145222676</v>
       </c>
     </row>
     <row r="60">
@@ -1937,16 +1937,16 @@
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="n">
-        <v>0.7543900410521138</v>
+        <v>0.7535956845953506</v>
       </c>
       <c r="D60" t="n">
-        <v>0.7543392026120677</v>
+        <v>0.7543582394464294</v>
       </c>
       <c r="E60" t="n">
-        <v>0.7544107972594583</v>
+        <v>0.7542317953169434</v>
       </c>
       <c r="F60" t="n">
-        <v>0.754019600444046</v>
+        <v>0.7543553449579044</v>
       </c>
     </row>
     <row r="61">
@@ -1955,16 +1955,16 @@
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="n">
-        <v>0.7543903620169436</v>
+        <v>0.7535956845953506</v>
       </c>
       <c r="D61" t="n">
-        <v>0.7543392767380381</v>
+        <v>0.7543588673130923</v>
       </c>
       <c r="E61" t="n">
-        <v>0.7544108457019491</v>
+        <v>0.7542317959397637</v>
       </c>
       <c r="F61" t="n">
-        <v>0.7540202654177295</v>
+        <v>0.7543554713533626</v>
       </c>
     </row>
     <row r="62">
@@ -1973,16 +1973,16 @@
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
-        <v>0.7543903620169436</v>
+        <v>0.7535961877429487</v>
       </c>
       <c r="D62" t="n">
-        <v>0.7543392767380381</v>
+        <v>0.7543588673130923</v>
       </c>
       <c r="E62" t="n">
-        <v>0.7544108661879441</v>
+        <v>0.7542317959397637</v>
       </c>
       <c r="F62" t="n">
-        <v>0.7540202654177295</v>
+        <v>0.7543554713533626</v>
       </c>
     </row>
     <row r="63">
@@ -1991,16 +1991,16 @@
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="n">
-        <v>0.754390362524509</v>
+        <v>0.7535965511717992</v>
       </c>
       <c r="D63" t="n">
-        <v>0.7543393535340585</v>
+        <v>0.7543591417227149</v>
       </c>
       <c r="E63" t="n">
-        <v>0.7544108785186667</v>
+        <v>0.7542317959397637</v>
       </c>
       <c r="F63" t="n">
-        <v>0.7540205238373547</v>
+        <v>0.754355744705597</v>
       </c>
     </row>
     <row r="64">
@@ -2009,16 +2009,16 @@
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="n">
-        <v>0.754390362524509</v>
+        <v>0.7535968089635183</v>
       </c>
       <c r="D64" t="n">
-        <v>0.7543393691169924</v>
+        <v>0.7543591717249871</v>
       </c>
       <c r="E64" t="n">
-        <v>0.7544108785186667</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F64" t="n">
-        <v>0.7540205238373547</v>
+        <v>0.7543560589207798</v>
       </c>
     </row>
     <row r="65">
@@ -2027,16 +2027,16 @@
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="n">
-        <v>0.754390362524509</v>
+        <v>0.7535968089635183</v>
       </c>
       <c r="D65" t="n">
-        <v>0.7543394152125977</v>
+        <v>0.7543591717249871</v>
       </c>
       <c r="E65" t="n">
-        <v>0.7544108804343633</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F65" t="n">
-        <v>0.7540212805262588</v>
+        <v>0.7543562381438695</v>
       </c>
     </row>
     <row r="66">
@@ -2045,16 +2045,16 @@
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="n">
-        <v>0.754390362524509</v>
+        <v>0.7535971994527317</v>
       </c>
       <c r="D66" t="n">
-        <v>0.7543394152125977</v>
+        <v>0.7543592355399954</v>
       </c>
       <c r="E66" t="n">
-        <v>0.7544108822388744</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F66" t="n">
-        <v>0.754021351760753</v>
+        <v>0.7543562381438695</v>
       </c>
     </row>
     <row r="67">
@@ -2063,16 +2063,16 @@
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="n">
-        <v>0.754390362524509</v>
+        <v>0.7535971994527317</v>
       </c>
       <c r="D67" t="n">
-        <v>0.7543394152125977</v>
+        <v>0.7543593105542508</v>
       </c>
       <c r="E67" t="n">
-        <v>0.7544108828450169</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F67" t="n">
-        <v>0.7540218118366613</v>
+        <v>0.7543563661159086</v>
       </c>
     </row>
     <row r="68">
@@ -2081,16 +2081,16 @@
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
-        <v>0.754390362524509</v>
+        <v>0.7535972249258673</v>
       </c>
       <c r="D68" t="n">
-        <v>0.7543394199288237</v>
+        <v>0.7543594880912818</v>
       </c>
       <c r="E68" t="n">
-        <v>0.7544108838343131</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F68" t="n">
-        <v>0.7540218414788158</v>
+        <v>0.7543563904102604</v>
       </c>
     </row>
     <row r="69">
@@ -2099,16 +2099,16 @@
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="n">
-        <v>0.754390363994955</v>
+        <v>0.7535972561501987</v>
       </c>
       <c r="D69" t="n">
-        <v>0.7543394235258916</v>
+        <v>0.7543595728169339</v>
       </c>
       <c r="E69" t="n">
-        <v>0.7544108846495279</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F69" t="n">
-        <v>0.7540218950771511</v>
+        <v>0.7543564503453319</v>
       </c>
     </row>
     <row r="70">
@@ -2117,16 +2117,16 @@
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="n">
-        <v>0.7543903747859768</v>
+        <v>0.7535973143601149</v>
       </c>
       <c r="D70" t="n">
-        <v>0.7543394246640892</v>
+        <v>0.7543595772429148</v>
       </c>
       <c r="E70" t="n">
-        <v>0.7544108846495279</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F70" t="n">
-        <v>0.7540220194060853</v>
+        <v>0.7543565114356785</v>
       </c>
     </row>
     <row r="71">
@@ -2135,16 +2135,16 @@
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="n">
-        <v>0.7543903753833989</v>
+        <v>0.7535973143601149</v>
       </c>
       <c r="D71" t="n">
-        <v>0.7543394246640892</v>
+        <v>0.7543596637879026</v>
       </c>
       <c r="E71" t="n">
-        <v>0.7544108846495279</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F71" t="n">
-        <v>0.7540222371222733</v>
+        <v>0.7543565114356785</v>
       </c>
     </row>
     <row r="72">
@@ -2153,16 +2153,16 @@
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="n">
-        <v>0.7543903753833989</v>
+        <v>0.753597321015837</v>
       </c>
       <c r="D72" t="n">
-        <v>0.7543394467306257</v>
+        <v>0.754389847709002</v>
       </c>
       <c r="E72" t="n">
-        <v>0.7544108846495279</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F72" t="n">
-        <v>0.7540222371222733</v>
+        <v>0.7543565114356785</v>
       </c>
     </row>
     <row r="73">
@@ -2171,16 +2171,16 @@
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="n">
-        <v>0.7543903753892852</v>
+        <v>0.753597321015837</v>
       </c>
       <c r="D73" t="n">
-        <v>0.7543394467306257</v>
+        <v>0.754389847709002</v>
       </c>
       <c r="E73" t="n">
-        <v>0.7544108850695256</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F73" t="n">
-        <v>0.754022269105427</v>
+        <v>0.754356520980733</v>
       </c>
     </row>
     <row r="74">
@@ -2189,16 +2189,16 @@
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="n">
-        <v>0.7543903753892852</v>
+        <v>0.7535973242902126</v>
       </c>
       <c r="D74" t="n">
-        <v>0.7543394467306257</v>
+        <v>0.754389847709002</v>
       </c>
       <c r="E74" t="n">
-        <v>0.7544108859717629</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F74" t="n">
-        <v>0.754022269105427</v>
+        <v>0.754356520980733</v>
       </c>
     </row>
     <row r="75">
@@ -2207,16 +2207,16 @@
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="n">
-        <v>0.7543903753892852</v>
+        <v>0.7535973242902126</v>
       </c>
       <c r="D75" t="n">
-        <v>0.7543394467306257</v>
+        <v>0.7543902597983179</v>
       </c>
       <c r="E75" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F75" t="n">
-        <v>0.754022269105427</v>
+        <v>0.754356544019561</v>
       </c>
     </row>
     <row r="76">
@@ -2225,16 +2225,16 @@
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="n">
-        <v>0.7543903753892852</v>
+        <v>0.7535973916842303</v>
       </c>
       <c r="D76" t="n">
-        <v>0.7543394467306257</v>
+        <v>0.7543903466777705</v>
       </c>
       <c r="E76" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F76" t="n">
-        <v>0.754022325606248</v>
+        <v>0.754356544019561</v>
       </c>
     </row>
     <row r="77">
@@ -2243,16 +2243,16 @@
       </c>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="n">
-        <v>0.7543903753892852</v>
+        <v>0.7542273063342642</v>
       </c>
       <c r="D77" t="n">
-        <v>0.7543394467306257</v>
+        <v>0.7543907869036954</v>
       </c>
       <c r="E77" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F77" t="n">
-        <v>0.754022325606248</v>
+        <v>0.7543565546303608</v>
       </c>
     </row>
     <row r="78">
@@ -2261,16 +2261,16 @@
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="n">
-        <v>0.7543903755859672</v>
+        <v>0.7542273063342642</v>
       </c>
       <c r="D78" t="n">
-        <v>0.7543394467306257</v>
+        <v>0.7543907869036954</v>
       </c>
       <c r="E78" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F78" t="n">
-        <v>0.754022325606248</v>
+        <v>0.7543565546303608</v>
       </c>
     </row>
     <row r="79">
@@ -2279,16 +2279,16 @@
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="n">
-        <v>0.7543903758092829</v>
+        <v>0.7542273063342642</v>
       </c>
       <c r="D79" t="n">
-        <v>0.7543394467306257</v>
+        <v>0.7543907974781601</v>
       </c>
       <c r="E79" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F79" t="n">
-        <v>0.7540223290473292</v>
+        <v>0.7543565546303608</v>
       </c>
     </row>
     <row r="80">
@@ -2297,16 +2297,16 @@
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="n">
-        <v>0.7543903758092829</v>
+        <v>0.7542273063342642</v>
       </c>
       <c r="D80" t="n">
-        <v>0.7543394467306257</v>
+        <v>0.7543908480845892</v>
       </c>
       <c r="E80" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F80" t="n">
-        <v>0.7540223290473292</v>
+        <v>0.7543565894645499</v>
       </c>
     </row>
     <row r="81">
@@ -2315,16 +2315,16 @@
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="n">
-        <v>0.7543903758092829</v>
+        <v>0.7542273063342642</v>
       </c>
       <c r="D81" t="n">
-        <v>0.7543394467306257</v>
+        <v>0.7543908532849806</v>
       </c>
       <c r="E81" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F81" t="n">
-        <v>0.7540223455672732</v>
+        <v>0.7543887919800565</v>
       </c>
     </row>
     <row r="82">
@@ -2333,13 +2333,13 @@
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="n">
-        <v>0.7543903758092829</v>
+        <v>0.7542273063342642</v>
       </c>
       <c r="D82" t="n">
-        <v>0.7543394467306257</v>
+        <v>0.7543908543046167</v>
       </c>
       <c r="E82" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F82" t="inlineStr"/>
     </row>
@@ -2349,13 +2349,13 @@
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
-        <v>0.7543903758092829</v>
+        <v>0.7542273537538126</v>
       </c>
       <c r="D83" t="n">
-        <v>0.75433948886712</v>
+        <v>0.7543908604931417</v>
       </c>
       <c r="E83" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F83" t="inlineStr"/>
     </row>
@@ -2365,13 +2365,13 @@
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="n">
-        <v>0.7543903758092829</v>
+        <v>0.7542274188277964</v>
       </c>
       <c r="D84" t="n">
-        <v>0.75433948886712</v>
+        <v>0.7543908938568848</v>
       </c>
       <c r="E84" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F84" t="inlineStr"/>
     </row>
@@ -2381,13 +2381,13 @@
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="n">
-        <v>0.7543903758092829</v>
+        <v>0.7542274211354763</v>
       </c>
       <c r="D85" t="n">
-        <v>0.75433948886712</v>
+        <v>0.7543908938568848</v>
       </c>
       <c r="E85" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F85" t="inlineStr"/>
     </row>
@@ -2397,13 +2397,13 @@
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="n">
-        <v>0.7543903758092829</v>
+        <v>0.7542274432270113</v>
       </c>
       <c r="D86" t="n">
-        <v>0.75433948886712</v>
+        <v>0.7543908940406679</v>
       </c>
       <c r="E86" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F86" t="inlineStr"/>
     </row>
@@ -2413,13 +2413,13 @@
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="n">
-        <v>0.7543903758092829</v>
+        <v>0.7542274483417972</v>
       </c>
       <c r="D87" t="n">
-        <v>0.75433948886712</v>
+        <v>0.7543908976028905</v>
       </c>
       <c r="E87" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F87" t="inlineStr"/>
     </row>
@@ -2429,13 +2429,13 @@
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="n">
-        <v>0.7543903758092829</v>
+        <v>0.7542274483417972</v>
       </c>
       <c r="D88" t="n">
-        <v>0.75433948886712</v>
+        <v>0.7543908976028905</v>
       </c>
       <c r="E88" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F88" t="inlineStr"/>
     </row>
@@ -2445,13 +2445,13 @@
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
-        <v>0.7543903758092829</v>
+        <v>0.7542274483417972</v>
       </c>
       <c r="D89" t="n">
-        <v>0.75433948886712</v>
+        <v>0.7543909059039757</v>
       </c>
       <c r="E89" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F89" t="inlineStr"/>
     </row>
@@ -2461,13 +2461,13 @@
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="n">
-        <v>0.7543903758092829</v>
+        <v>0.7542274579557431</v>
       </c>
       <c r="D90" t="n">
-        <v>0.75433948886712</v>
+        <v>0.7543909059039757</v>
       </c>
       <c r="E90" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F90" t="inlineStr"/>
     </row>
@@ -2477,13 +2477,13 @@
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
-        <v>0.7543903758092829</v>
+        <v>0.7542274611048352</v>
       </c>
       <c r="D91" t="n">
-        <v>0.75433948886712</v>
+        <v>0.7543909059039757</v>
       </c>
       <c r="E91" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F91" t="inlineStr"/>
     </row>
@@ -2493,13 +2493,13 @@
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
-        <v>0.7543903758092829</v>
+        <v>0.7542274611048352</v>
       </c>
       <c r="D92" t="n">
-        <v>0.75433948886712</v>
+        <v>0.754390915000037</v>
       </c>
       <c r="E92" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F92" t="inlineStr"/>
     </row>
@@ -2509,13 +2509,13 @@
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
-        <v>0.7543903758092829</v>
+        <v>0.7542274611048352</v>
       </c>
       <c r="D93" t="n">
-        <v>0.75433948886712</v>
+        <v>0.7543909160669451</v>
       </c>
       <c r="E93" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F93" t="inlineStr"/>
     </row>
@@ -2525,13 +2525,13 @@
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
-        <v>0.7543903758092829</v>
+        <v>0.7542274611048352</v>
       </c>
       <c r="D94" t="n">
-        <v>0.7543597095953337</v>
+        <v>0.7543909228390848</v>
       </c>
       <c r="E94" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F94" t="inlineStr"/>
     </row>
@@ -2541,13 +2541,13 @@
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>0.7543903758092829</v>
+        <v>0.7542274611048352</v>
       </c>
       <c r="D95" t="n">
-        <v>0.7543597095953337</v>
+        <v>0.7543909228390848</v>
       </c>
       <c r="E95" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F95" t="inlineStr"/>
     </row>
@@ -2557,13 +2557,13 @@
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
-        <v>0.7543903758092829</v>
+        <v>0.7542274611048352</v>
       </c>
       <c r="D96" t="n">
-        <v>0.7543599960898345</v>
+        <v>0.7543909228390848</v>
       </c>
       <c r="E96" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F96" t="inlineStr"/>
     </row>
@@ -2573,13 +2573,13 @@
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
-        <v>0.7543903758092829</v>
+        <v>0.7542274611048352</v>
       </c>
       <c r="D97" t="n">
-        <v>0.7543601298902081</v>
+        <v>0.754390924476091</v>
       </c>
       <c r="E97" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F97" t="inlineStr"/>
     </row>
@@ -2589,13 +2589,13 @@
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="n">
-        <v>0.7543903758092829</v>
+        <v>0.7542274611048352</v>
       </c>
       <c r="D98" t="n">
-        <v>0.7543602884897733</v>
+        <v>0.754390924476091</v>
       </c>
       <c r="E98" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F98" t="inlineStr"/>
     </row>
@@ -2605,13 +2605,13 @@
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="n">
-        <v>0.7543903758092829</v>
+        <v>0.7542274611048352</v>
       </c>
       <c r="D99" t="n">
-        <v>0.7543604625399039</v>
+        <v>0.754390924476091</v>
       </c>
       <c r="E99" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F99" t="inlineStr"/>
     </row>
@@ -2621,13 +2621,13 @@
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="n">
-        <v>0.7543903758092829</v>
+        <v>0.7542274611048352</v>
       </c>
       <c r="D100" t="n">
-        <v>0.7543604625399039</v>
+        <v>0.754390924476091</v>
       </c>
       <c r="E100" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F100" t="inlineStr"/>
     </row>
@@ -2637,13 +2637,13 @@
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="n">
-        <v>0.7543903758092829</v>
+        <v>0.7542274611048352</v>
       </c>
       <c r="D101" t="n">
-        <v>0.7543605384729287</v>
+        <v>0.7543909253678276</v>
       </c>
       <c r="E101" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F101" t="inlineStr"/>
     </row>
@@ -2654,10 +2654,10 @@
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="n">
-        <v>0.7543605384729287</v>
+        <v>0.7543909265118751</v>
       </c>
       <c r="E102" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F102" t="inlineStr"/>
     </row>
@@ -2668,10 +2668,10 @@
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="n">
-        <v>0.7543605384729287</v>
+        <v>0.754390926875844</v>
       </c>
       <c r="E103" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F103" t="inlineStr"/>
     </row>
@@ -2682,10 +2682,10 @@
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="n">
-        <v>0.7543605592965497</v>
+        <v>0.754390926875844</v>
       </c>
       <c r="E104" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F104" t="inlineStr"/>
     </row>
@@ -2696,10 +2696,10 @@
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="n">
-        <v>0.7543606595928903</v>
+        <v>0.754390926875844</v>
       </c>
       <c r="E105" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F105" t="inlineStr"/>
     </row>
@@ -2710,10 +2710,10 @@
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="n">
-        <v>0.7543606595928903</v>
+        <v>0.754390926875844</v>
       </c>
       <c r="E106" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F106" t="inlineStr"/>
     </row>
@@ -2724,10 +2724,10 @@
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="n">
-        <v>0.754360682672232</v>
+        <v>0.754390926875844</v>
       </c>
       <c r="E107" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F107" t="inlineStr"/>
     </row>
@@ -2738,10 +2738,10 @@
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="n">
-        <v>0.754360682672232</v>
+        <v>0.754390926875844</v>
       </c>
       <c r="E108" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F108" t="inlineStr"/>
     </row>
@@ -2752,10 +2752,10 @@
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="n">
-        <v>0.7543606921729211</v>
+        <v>0.754390926875844</v>
       </c>
       <c r="E109" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F109" t="inlineStr"/>
     </row>
@@ -2766,10 +2766,10 @@
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="n">
-        <v>0.7543606921729211</v>
+        <v>0.754390926875844</v>
       </c>
       <c r="E110" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F110" t="inlineStr"/>
     </row>
@@ -2780,10 +2780,10 @@
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="n">
-        <v>0.7543607079561705</v>
+        <v>0.754390926875844</v>
       </c>
       <c r="E111" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F111" t="inlineStr"/>
     </row>
@@ -2794,10 +2794,10 @@
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="n">
-        <v>0.7543607291528078</v>
+        <v>0.754390926875844</v>
       </c>
       <c r="E112" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F112" t="inlineStr"/>
     </row>
@@ -2808,10 +2808,10 @@
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="n">
-        <v>0.7543607312049792</v>
+        <v>0.754390926875844</v>
       </c>
       <c r="E113" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F113" t="inlineStr"/>
     </row>
@@ -2822,10 +2822,10 @@
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="n">
-        <v>0.7543607378593566</v>
+        <v>0.754390926875844</v>
       </c>
       <c r="E114" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F114" t="inlineStr"/>
     </row>
@@ -2836,10 +2836,10 @@
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="n">
-        <v>0.7543607751911492</v>
+        <v>0.754390926875844</v>
       </c>
       <c r="E115" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F115" t="inlineStr"/>
     </row>
@@ -2850,10 +2850,10 @@
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="n">
-        <v>0.7543607751911492</v>
+        <v>0.754390926875844</v>
       </c>
       <c r="E116" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F116" t="inlineStr"/>
     </row>
@@ -2864,10 +2864,10 @@
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="n">
-        <v>0.7543607801549261</v>
+        <v>0.754390926875844</v>
       </c>
       <c r="E117" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F117" t="inlineStr"/>
     </row>
@@ -2878,10 +2878,10 @@
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="n">
-        <v>0.7543607801549261</v>
+        <v>0.754390926875844</v>
       </c>
       <c r="E118" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F118" t="inlineStr"/>
     </row>
@@ -2892,10 +2892,10 @@
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="n">
-        <v>0.7543607801549261</v>
+        <v>0.754390926875844</v>
       </c>
       <c r="E119" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F119" t="inlineStr"/>
     </row>
@@ -2906,10 +2906,10 @@
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="n">
-        <v>0.7543607801549261</v>
+        <v>0.754390926875844</v>
       </c>
       <c r="E120" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F120" t="inlineStr"/>
     </row>
@@ -2920,10 +2920,10 @@
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="n">
-        <v>0.7543607801549261</v>
+        <v>0.754390926875844</v>
       </c>
       <c r="E121" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F121" t="inlineStr"/>
     </row>
@@ -2934,10 +2934,10 @@
       <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="n">
-        <v>0.7543607801549261</v>
+        <v>0.754390926875844</v>
       </c>
       <c r="E122" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F122" t="inlineStr"/>
     </row>
@@ -2948,10 +2948,10 @@
       <c r="B123" t="inlineStr"/>
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="n">
-        <v>0.7543607817497109</v>
+        <v>0.754390926875844</v>
       </c>
       <c r="E123" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F123" t="inlineStr"/>
     </row>
@@ -2962,10 +2962,10 @@
       <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="n">
-        <v>0.7543607817497109</v>
+        <v>0.754390926875844</v>
       </c>
       <c r="E124" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F124" t="inlineStr"/>
     </row>
@@ -2976,10 +2976,10 @@
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="n">
-        <v>0.7543607817497109</v>
+        <v>0.754390926875844</v>
       </c>
       <c r="E125" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F125" t="inlineStr"/>
     </row>
@@ -2990,10 +2990,10 @@
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="n">
-        <v>0.7543607821697087</v>
+        <v>0.754390926875844</v>
       </c>
       <c r="E126" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F126" t="inlineStr"/>
     </row>
@@ -3004,10 +3004,10 @@
       <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="n">
-        <v>0.7543607821697087</v>
+        <v>0.754390926875844</v>
       </c>
       <c r="E127" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F127" t="inlineStr"/>
     </row>
@@ -3018,10 +3018,10 @@
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="n">
-        <v>0.7543607821697087</v>
+        <v>0.754390926875844</v>
       </c>
       <c r="E128" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F128" t="inlineStr"/>
     </row>
@@ -3032,10 +3032,10 @@
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="n">
-        <v>0.7543607821697087</v>
+        <v>0.754390926875844</v>
       </c>
       <c r="E129" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F129" t="inlineStr"/>
     </row>
@@ -3046,10 +3046,10 @@
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="n">
-        <v>0.7543607833669508</v>
+        <v>0.754390926875844</v>
       </c>
       <c r="E130" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F130" t="inlineStr"/>
     </row>
@@ -3060,10 +3060,10 @@
       <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="n">
-        <v>0.7543607833669508</v>
+        <v>0.754390926875844</v>
       </c>
       <c r="E131" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F131" t="inlineStr"/>
     </row>
@@ -3074,10 +3074,10 @@
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="n">
-        <v>0.7543607859763575</v>
+        <v>0.754390926875844</v>
       </c>
       <c r="E132" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F132" t="inlineStr"/>
     </row>
@@ -3088,10 +3088,10 @@
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="n">
-        <v>0.7543607859763575</v>
+        <v>0.754390926875844</v>
       </c>
       <c r="E133" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F133" t="inlineStr"/>
     </row>
@@ -3102,10 +3102,10 @@
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="n">
-        <v>0.7543607859763575</v>
+        <v>0.754390926875844</v>
       </c>
       <c r="E134" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F134" t="inlineStr"/>
     </row>
@@ -3116,10 +3116,10 @@
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="n">
-        <v>0.7543607859763575</v>
+        <v>0.754390926875844</v>
       </c>
       <c r="E135" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F135" t="inlineStr"/>
     </row>
@@ -3130,10 +3130,10 @@
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="n">
-        <v>0.7543607859763575</v>
+        <v>0.754390926875844</v>
       </c>
       <c r="E136" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F136" t="inlineStr"/>
     </row>
@@ -3144,10 +3144,10 @@
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="n">
-        <v>0.7543607863280088</v>
+        <v>0.754390926875844</v>
       </c>
       <c r="E137" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F137" t="inlineStr"/>
     </row>
@@ -3158,10 +3158,10 @@
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="n">
-        <v>0.7543607863280088</v>
+        <v>0.754390926875844</v>
       </c>
       <c r="E138" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F138" t="inlineStr"/>
     </row>
@@ -3172,10 +3172,10 @@
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="n">
-        <v>0.7543607863280088</v>
+        <v>0.754390926875844</v>
       </c>
       <c r="E139" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F139" t="inlineStr"/>
     </row>
@@ -3186,10 +3186,10 @@
       <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="n">
-        <v>0.7543607863280088</v>
+        <v>0.754390926875844</v>
       </c>
       <c r="E140" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F140" t="inlineStr"/>
     </row>
@@ -3200,10 +3200,10 @@
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="n">
-        <v>0.7543607863280088</v>
+        <v>0.754390926875844</v>
       </c>
       <c r="E141" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F141" t="inlineStr"/>
     </row>
@@ -3214,10 +3214,10 @@
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="n">
-        <v>0.7543607863280088</v>
+        <v>0.754390926875844</v>
       </c>
       <c r="E142" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F142" t="inlineStr"/>
     </row>
@@ -3228,10 +3228,10 @@
       <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="n">
-        <v>0.7543607863280088</v>
+        <v>0.754390926875844</v>
       </c>
       <c r="E143" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F143" t="inlineStr"/>
     </row>
@@ -3242,10 +3242,10 @@
       <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="n">
-        <v>0.7543607863280088</v>
+        <v>0.754390926875844</v>
       </c>
       <c r="E144" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F144" t="inlineStr"/>
     </row>
@@ -3256,10 +3256,10 @@
       <c r="B145" t="inlineStr"/>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="n">
-        <v>0.7543607863280088</v>
+        <v>0.754390926875844</v>
       </c>
       <c r="E145" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F145" t="inlineStr"/>
     </row>
@@ -3270,10 +3270,10 @@
       <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="n">
-        <v>0.7543607863280088</v>
+        <v>0.754390926875844</v>
       </c>
       <c r="E146" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F146" t="inlineStr"/>
     </row>
@@ -3284,10 +3284,10 @@
       <c r="B147" t="inlineStr"/>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="n">
-        <v>0.7543607863280088</v>
+        <v>0.754390926875844</v>
       </c>
       <c r="E147" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F147" t="inlineStr"/>
     </row>
@@ -3298,10 +3298,10 @@
       <c r="B148" t="inlineStr"/>
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="n">
-        <v>0.7543607863280088</v>
+        <v>0.754390926875844</v>
       </c>
       <c r="E148" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F148" t="inlineStr"/>
     </row>
@@ -3312,10 +3312,10 @@
       <c r="B149" t="inlineStr"/>
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="n">
-        <v>0.7543607863280088</v>
+        <v>0.754390926875844</v>
       </c>
       <c r="E149" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F149" t="inlineStr"/>
     </row>
@@ -3326,10 +3326,10 @@
       <c r="B150" t="inlineStr"/>
       <c r="C150" t="inlineStr"/>
       <c r="D150" t="n">
-        <v>0.7543607863280088</v>
+        <v>0.754390926875844</v>
       </c>
       <c r="E150" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F150" t="inlineStr"/>
     </row>
@@ -3340,10 +3340,10 @@
       <c r="B151" t="inlineStr"/>
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="n">
-        <v>0.7543607863280088</v>
+        <v>0.754390926875844</v>
       </c>
       <c r="E151" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F151" t="inlineStr"/>
     </row>
@@ -3355,7 +3355,7 @@
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F152" t="inlineStr"/>
     </row>
@@ -3367,7 +3367,7 @@
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F153" t="inlineStr"/>
     </row>
@@ -3379,7 +3379,7 @@
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F154" t="inlineStr"/>
     </row>
@@ -3391,7 +3391,7 @@
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F155" t="inlineStr"/>
     </row>
@@ -3403,7 +3403,7 @@
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F156" t="inlineStr"/>
     </row>
@@ -3415,7 +3415,7 @@
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7542318039895188</v>
       </c>
       <c r="F157" t="inlineStr"/>
     </row>
@@ -3427,7 +3427,7 @@
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7543522213130777</v>
       </c>
       <c r="F158" t="inlineStr"/>
     </row>
@@ -3439,7 +3439,7 @@
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr"/>
       <c r="E159" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7543522213130777</v>
       </c>
       <c r="F159" t="inlineStr"/>
     </row>
@@ -3451,7 +3451,7 @@
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7543522213130777</v>
       </c>
       <c r="F160" t="inlineStr"/>
     </row>
@@ -3463,7 +3463,7 @@
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7543522213130777</v>
       </c>
       <c r="F161" t="inlineStr"/>
     </row>
@@ -3475,7 +3475,7 @@
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7543522213130777</v>
       </c>
       <c r="F162" t="inlineStr"/>
     </row>
@@ -3487,7 +3487,7 @@
       <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7543522213130777</v>
       </c>
       <c r="F163" t="inlineStr"/>
     </row>
@@ -3499,7 +3499,7 @@
       <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7543522213130777</v>
       </c>
       <c r="F164" t="inlineStr"/>
     </row>
@@ -3511,7 +3511,7 @@
       <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr"/>
       <c r="E165" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7543522239980613</v>
       </c>
       <c r="F165" t="inlineStr"/>
     </row>
@@ -3523,7 +3523,7 @@
       <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr"/>
       <c r="E166" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7543522309277502</v>
       </c>
       <c r="F166" t="inlineStr"/>
     </row>
@@ -3535,7 +3535,7 @@
       <c r="C167" t="inlineStr"/>
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7543522418690906</v>
       </c>
       <c r="F167" t="inlineStr"/>
     </row>
@@ -3547,7 +3547,7 @@
       <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7543522418690906</v>
       </c>
       <c r="F168" t="inlineStr"/>
     </row>
@@ -3559,7 +3559,7 @@
       <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr"/>
       <c r="E169" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7543522727407531</v>
       </c>
       <c r="F169" t="inlineStr"/>
     </row>
@@ -3571,7 +3571,7 @@
       <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr"/>
       <c r="E170" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7543522819891676</v>
       </c>
       <c r="F170" t="inlineStr"/>
     </row>
@@ -3583,7 +3583,7 @@
       <c r="C171" t="inlineStr"/>
       <c r="D171" t="inlineStr"/>
       <c r="E171" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7543522840461351</v>
       </c>
       <c r="F171" t="inlineStr"/>
     </row>
@@ -3595,7 +3595,7 @@
       <c r="C172" t="inlineStr"/>
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7543522840461351</v>
       </c>
       <c r="F172" t="inlineStr"/>
     </row>
@@ -3607,7 +3607,7 @@
       <c r="C173" t="inlineStr"/>
       <c r="D173" t="inlineStr"/>
       <c r="E173" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7543522859649928</v>
       </c>
       <c r="F173" t="inlineStr"/>
     </row>
@@ -3619,7 +3619,7 @@
       <c r="C174" t="inlineStr"/>
       <c r="D174" t="inlineStr"/>
       <c r="E174" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7543522859649928</v>
       </c>
       <c r="F174" t="inlineStr"/>
     </row>
@@ -3631,7 +3631,7 @@
       <c r="C175" t="inlineStr"/>
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7543522859649928</v>
       </c>
       <c r="F175" t="inlineStr"/>
     </row>
@@ -3643,7 +3643,7 @@
       <c r="C176" t="inlineStr"/>
       <c r="D176" t="inlineStr"/>
       <c r="E176" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7543522859649928</v>
       </c>
       <c r="F176" t="inlineStr"/>
     </row>
@@ -3655,7 +3655,7 @@
       <c r="C177" t="inlineStr"/>
       <c r="D177" t="inlineStr"/>
       <c r="E177" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.7543522885953284</v>
       </c>
       <c r="F177" t="inlineStr"/>
     </row>
@@ -3667,7 +3667,7 @@
       <c r="C178" t="inlineStr"/>
       <c r="D178" t="inlineStr"/>
       <c r="E178" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.754352294149079</v>
       </c>
       <c r="F178" t="inlineStr"/>
     </row>
@@ -3679,7 +3679,7 @@
       <c r="C179" t="inlineStr"/>
       <c r="D179" t="inlineStr"/>
       <c r="E179" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.754352294149079</v>
       </c>
       <c r="F179" t="inlineStr"/>
     </row>
@@ -3691,7 +3691,7 @@
       <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr"/>
       <c r="E180" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.754352294149079</v>
       </c>
       <c r="F180" t="inlineStr"/>
     </row>
@@ -3703,7 +3703,7 @@
       <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr"/>
       <c r="E181" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.754352294149079</v>
       </c>
       <c r="F181" t="inlineStr"/>
     </row>
@@ -3715,7 +3715,7 @@
       <c r="C182" t="inlineStr"/>
       <c r="D182" t="inlineStr"/>
       <c r="E182" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.754352294149079</v>
       </c>
       <c r="F182" t="inlineStr"/>
     </row>
@@ -3727,7 +3727,7 @@
       <c r="C183" t="inlineStr"/>
       <c r="D183" t="inlineStr"/>
       <c r="E183" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.754352294149079</v>
       </c>
       <c r="F183" t="inlineStr"/>
     </row>
@@ -3739,7 +3739,7 @@
       <c r="C184" t="inlineStr"/>
       <c r="D184" t="inlineStr"/>
       <c r="E184" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.754352294149079</v>
       </c>
       <c r="F184" t="inlineStr"/>
     </row>
@@ -3751,7 +3751,7 @@
       <c r="C185" t="inlineStr"/>
       <c r="D185" t="inlineStr"/>
       <c r="E185" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.754352294149079</v>
       </c>
       <c r="F185" t="inlineStr"/>
     </row>
@@ -3763,7 +3763,7 @@
       <c r="C186" t="inlineStr"/>
       <c r="D186" t="inlineStr"/>
       <c r="E186" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.754352294149079</v>
       </c>
       <c r="F186" t="inlineStr"/>
     </row>
@@ -3775,7 +3775,7 @@
       <c r="C187" t="inlineStr"/>
       <c r="D187" t="inlineStr"/>
       <c r="E187" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.754352294149079</v>
       </c>
       <c r="F187" t="inlineStr"/>
     </row>
@@ -3787,7 +3787,7 @@
       <c r="C188" t="inlineStr"/>
       <c r="D188" t="inlineStr"/>
       <c r="E188" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.754352294149079</v>
       </c>
       <c r="F188" t="inlineStr"/>
     </row>
@@ -3799,7 +3799,7 @@
       <c r="C189" t="inlineStr"/>
       <c r="D189" t="inlineStr"/>
       <c r="E189" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.754352294149079</v>
       </c>
       <c r="F189" t="inlineStr"/>
     </row>
@@ -3811,7 +3811,7 @@
       <c r="C190" t="inlineStr"/>
       <c r="D190" t="inlineStr"/>
       <c r="E190" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.754352294149079</v>
       </c>
       <c r="F190" t="inlineStr"/>
     </row>
@@ -3823,7 +3823,7 @@
       <c r="C191" t="inlineStr"/>
       <c r="D191" t="inlineStr"/>
       <c r="E191" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.754352294149079</v>
       </c>
       <c r="F191" t="inlineStr"/>
     </row>
@@ -3835,7 +3835,7 @@
       <c r="C192" t="inlineStr"/>
       <c r="D192" t="inlineStr"/>
       <c r="E192" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.754352294149079</v>
       </c>
       <c r="F192" t="inlineStr"/>
     </row>
@@ -3847,7 +3847,7 @@
       <c r="C193" t="inlineStr"/>
       <c r="D193" t="inlineStr"/>
       <c r="E193" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.754352294149079</v>
       </c>
       <c r="F193" t="inlineStr"/>
     </row>
@@ -3859,7 +3859,7 @@
       <c r="C194" t="inlineStr"/>
       <c r="D194" t="inlineStr"/>
       <c r="E194" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.754352294149079</v>
       </c>
       <c r="F194" t="inlineStr"/>
     </row>
@@ -3871,7 +3871,7 @@
       <c r="C195" t="inlineStr"/>
       <c r="D195" t="inlineStr"/>
       <c r="E195" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.754352294149079</v>
       </c>
       <c r="F195" t="inlineStr"/>
     </row>
@@ -3883,7 +3883,7 @@
       <c r="C196" t="inlineStr"/>
       <c r="D196" t="inlineStr"/>
       <c r="E196" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.754352294149079</v>
       </c>
       <c r="F196" t="inlineStr"/>
     </row>
@@ -3895,7 +3895,7 @@
       <c r="C197" t="inlineStr"/>
       <c r="D197" t="inlineStr"/>
       <c r="E197" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.754352294149079</v>
       </c>
       <c r="F197" t="inlineStr"/>
     </row>
@@ -3907,7 +3907,7 @@
       <c r="C198" t="inlineStr"/>
       <c r="D198" t="inlineStr"/>
       <c r="E198" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.754352294149079</v>
       </c>
       <c r="F198" t="inlineStr"/>
     </row>
@@ -3919,7 +3919,7 @@
       <c r="C199" t="inlineStr"/>
       <c r="D199" t="inlineStr"/>
       <c r="E199" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.754352294149079</v>
       </c>
       <c r="F199" t="inlineStr"/>
     </row>
@@ -3931,7 +3931,7 @@
       <c r="C200" t="inlineStr"/>
       <c r="D200" t="inlineStr"/>
       <c r="E200" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.754352294149079</v>
       </c>
       <c r="F200" t="inlineStr"/>
     </row>
@@ -3943,7 +3943,7 @@
       <c r="C201" t="inlineStr"/>
       <c r="D201" t="inlineStr"/>
       <c r="E201" t="n">
-        <v>0.7544108862449668</v>
+        <v>0.754352294149079</v>
       </c>
       <c r="F201" t="inlineStr"/>
     </row>
